--- a/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
@@ -235,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O84" headerRowCount="1">
-  <autoFilter ref="A1:O84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O137" headerRowCount="1">
+  <autoFilter ref="A1:O137"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -4927,7 +4927,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5087,7 +5086,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5329,7 +5327,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5448,7 +5445,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5649,7 +5645,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5727,7 +5722,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5928,7 +5922,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6006,7 +5999,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6043,7 +6035,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6162,7 +6153,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6209,7 +6199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="13" min="1" max="2"/>
@@ -9515,18 +9505,2108 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp2</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp11</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp12</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp15</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp3</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp6</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp18</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp19</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp3</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Madawaki</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp4</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp5</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp21</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Kareram</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hoyo Chingua</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp3</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ardoram</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp4</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hoyo Chingua</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp13</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ardoram</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp14</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hoyo Chingua</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp5</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gubio 1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp6</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hoyo Chingua</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp7</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ardoram</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp10</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp12</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp6</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Gubio 1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp17</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kareram</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>non_idp_NG008020_supp18</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp25</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp26</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Bena</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp27</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mayanchi</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>non_idp_NG037010_supp28</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Bolori 1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>non_idp_NG008021_supp1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bolori 1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>non_idp_NG008021_supp2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Bolori 2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>non_idp_NG008021_supp3</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp8</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp3</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp4</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp5</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp6</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>idp_NG008020_supp7</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Maisandari</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>idp_NG008021_supp1</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mafoni</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>idp_NG008021_supp2</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bolori 2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>idp_NG008021_supp3</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bolori 2</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>idp_NG008021_supp4</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Bolori 2</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>idp_NG008021_supp5</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp5</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sabon Gari</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp6</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp7</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp8</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp1</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp2</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>idp_NG037007_supp4</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9793,13 +11873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A454C7-AC2D-426D-8545-B0FEE9F1FB85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C026B7B-8191-46C2-8A05-07C879F7693D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82BBFDDA-6FB0-4344-8991-69603B962350}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42FA76A3-DC1F-4F6C-9D79-A10BDEA9079A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7765FD9E-3822-48C0-B2B2-627834A0CEA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A88E41A-EB63-4019-8ADC-D48E1E949D5E}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
@@ -235,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O137" headerRowCount="1">
-  <autoFilter ref="A1:O137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O139" headerRowCount="1">
+  <autoFilter ref="A1:O139"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -6199,7 +6199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="13" min="1" max="2"/>
@@ -9531,7 +9531,6 @@
           <t>non_idp_NG037010_supp2</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>6</t>
@@ -9569,7 +9568,6 @@
           <t>non_idp_NG037010_supp11</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>6</t>
@@ -9607,7 +9605,6 @@
           <t>non_idp_NG037010_supp12</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>6</t>
@@ -9645,7 +9642,6 @@
           <t>non_idp_NG037010_supp15</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>6</t>
@@ -9683,7 +9679,6 @@
           <t>non_idp_NG037010_supp3</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>6</t>
@@ -9721,7 +9716,6 @@
           <t>non_idp_NG037010_supp4</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>6</t>
@@ -9759,7 +9753,6 @@
           <t>non_idp_NG037010_supp6</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>6</t>
@@ -9797,7 +9790,6 @@
           <t>non_idp_NG037010_supp18</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>6</t>
@@ -9835,7 +9827,6 @@
           <t>non_idp_NG037010_supp19</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>6</t>
@@ -9873,7 +9864,6 @@
           <t>non_idp_NG037007_supp3</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>6</t>
@@ -9911,7 +9901,6 @@
           <t>non_idp_NG037007_supp4</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>6</t>
@@ -9949,7 +9938,6 @@
           <t>non_idp_NG037007_supp5</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>6</t>
@@ -9987,7 +9975,6 @@
           <t>non_idp_NG037010_supp21</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>6</t>
@@ -10025,7 +10012,6 @@
           <t>non_idp_NG008020_supp1</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>6</t>
@@ -10063,7 +10049,6 @@
           <t>non_idp_NG008020_supp3</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>6</t>
@@ -10101,7 +10086,6 @@
           <t>non_idp_NG008020_supp4</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>6</t>
@@ -10139,7 +10123,6 @@
           <t>non_idp_NG008020_supp13</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>6</t>
@@ -10177,7 +10160,6 @@
           <t>non_idp_NG008020_supp14</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>6</t>
@@ -10215,7 +10197,6 @@
           <t>non_idp_NG008020_supp5</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>6</t>
@@ -10253,7 +10234,6 @@
           <t>non_idp_NG008020_supp6</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>6</t>
@@ -10291,7 +10271,6 @@
           <t>non_idp_NG008020_supp7</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>6</t>
@@ -10329,7 +10308,6 @@
           <t>non_idp_NG008020_supp10</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>6</t>
@@ -10367,7 +10345,6 @@
           <t>non_idp_NG008020_supp12</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>6</t>
@@ -10405,7 +10382,6 @@
           <t>non_idp_NG037007_supp6</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>6</t>
@@ -10443,7 +10419,6 @@
           <t>non_idp_NG008020_supp17</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>6</t>
@@ -10481,7 +10456,6 @@
           <t>non_idp_NG008020_supp18</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>6</t>
@@ -10519,7 +10493,6 @@
           <t>non_idp_NG037010_supp25</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>6</t>
@@ -10557,7 +10530,6 @@
           <t>non_idp_NG037010_supp26</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>6</t>
@@ -10595,7 +10567,6 @@
           <t>non_idp_NG037010_supp27</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>6</t>
@@ -10633,7 +10604,6 @@
           <t>non_idp_NG037010_supp28</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>6</t>
@@ -10671,7 +10641,6 @@
           <t>non_idp_NG008021_supp1</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>6</t>
@@ -10709,7 +10678,6 @@
           <t>non_idp_NG008021_supp2</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>6</t>
@@ -10747,7 +10715,6 @@
           <t>non_idp_NG008021_supp3</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>6</t>
@@ -10785,7 +10752,6 @@
           <t>non_idp_NG037007_supp8</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>6</t>
@@ -11595,18 +11561,94 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp13</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>non_idp_NG037007_supp14</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11615,271 +11657,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C026B7B-8191-46C2-8A05-07C879F7693D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42FA76A3-DC1F-4F6C-9D79-A10BDEA9079A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A88E41A-EB63-4019-8ADC-D48E1E949D5E}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/INTERSOS_accessibility_report.xlsx
@@ -11657,4 +11657,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A550110A-F77F-4C6A-B17B-786C384A451F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA66B53A-317A-4542-B54A-A2D9E7D766FC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34CB9442-6823-47F2-A841-A5D1DC7F3E98}"/>
 </file>